--- a/record_list_all_pkg.xlsx
+++ b/record_list_all_pkg.xlsx
@@ -1,13 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uu\Desktop\大创\support_materials\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3536AB2-0177-4537-A46D-80892DF678D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$618</definedName>
@@ -21,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -30,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8655" uniqueCount="768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8951" uniqueCount="768">
   <si>
     <t>package name</t>
   </si>
@@ -2340,15 +2345,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2360,349 +2361,27 @@
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2725,253 +2404,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2982,68 +2419,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3328,33 +2721,34 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:O618"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="20.9833333333333" customWidth="1"/>
-    <col min="2" max="2" width="15.5833333333333" customWidth="1"/>
-    <col min="3" max="3" width="9.08333333333333" customWidth="1"/>
-    <col min="4" max="4" width="24.575" customWidth="1"/>
-    <col min="5" max="5" width="26.6416666666667" customWidth="1"/>
-    <col min="6" max="6" width="43.5083333333333" customWidth="1"/>
-    <col min="7" max="7" width="23.2583333333333" customWidth="1"/>
-    <col min="8" max="8" width="26.9666666666667" customWidth="1"/>
-    <col min="9" max="9" width="36.3" customWidth="1"/>
-    <col min="10" max="10" width="37.9916666666667" customWidth="1"/>
-    <col min="11" max="11" width="38.5416666666667" customWidth="1"/>
-    <col min="12" max="12" width="24.9583333333333" customWidth="1"/>
-    <col min="13" max="13" width="16.3" customWidth="1"/>
-    <col min="14" max="14" width="20.0916666666667" customWidth="1"/>
-    <col min="15" max="15" width="27.4583333333333" customWidth="1"/>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="15.625" customWidth="1"/>
+    <col min="3" max="3" width="12.125" customWidth="1"/>
+    <col min="4" max="4" width="24.625" customWidth="1"/>
+    <col min="5" max="5" width="26.625" customWidth="1"/>
+    <col min="6" max="6" width="43.5" customWidth="1"/>
+    <col min="7" max="7" width="23.25" customWidth="1"/>
+    <col min="8" max="8" width="27" customWidth="1"/>
+    <col min="9" max="9" width="36.25" customWidth="1"/>
+    <col min="10" max="10" width="38" customWidth="1"/>
+    <col min="11" max="11" width="38.5" customWidth="1"/>
+    <col min="12" max="12" width="25" customWidth="1"/>
+    <col min="13" max="13" width="16.25" customWidth="1"/>
+    <col min="14" max="14" width="20.125" customWidth="1"/>
+    <col min="15" max="15" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3401,7 +2795,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>15</v>
       </c>
@@ -3448,7 +2842,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" hidden="1" spans="1:14">
+    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>29</v>
       </c>
@@ -3492,7 +2886,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>33</v>
       </c>
@@ -3539,7 +2933,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1" spans="1:15">
+    <row r="5" spans="1:15" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>43</v>
       </c>
@@ -3586,7 +2980,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>52</v>
       </c>
@@ -3633,7 +3027,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>53</v>
       </c>
@@ -3680,7 +3074,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>54</v>
       </c>
@@ -3727,7 +3121,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" hidden="1" spans="1:14">
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>55</v>
       </c>
@@ -3771,7 +3165,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" hidden="1" spans="1:14">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>57</v>
       </c>
@@ -3815,7 +3209,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>58</v>
       </c>
@@ -3862,7 +3256,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" hidden="1" spans="1:14">
+    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>59</v>
       </c>
@@ -3906,7 +3300,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" hidden="1" spans="1:14">
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>60</v>
       </c>
@@ -3950,7 +3344,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" hidden="1" spans="1:14">
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>61</v>
       </c>
@@ -3994,7 +3388,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" hidden="1" spans="1:14">
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>62</v>
       </c>
@@ -4038,7 +3432,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" hidden="1" spans="1:14">
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>64</v>
       </c>
@@ -4082,7 +3476,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" hidden="1" spans="1:14">
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>65</v>
       </c>
@@ -4126,7 +3520,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" hidden="1" spans="1:14">
+    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>66</v>
       </c>
@@ -4170,7 +3564,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" hidden="1" spans="1:14">
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>67</v>
       </c>
@@ -4214,7 +3608,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>68</v>
       </c>
@@ -4261,7 +3655,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" hidden="1" spans="1:14">
+    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>69</v>
       </c>
@@ -4305,7 +3699,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" hidden="1" spans="1:14">
+    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
         <v>70</v>
       </c>
@@ -4349,7 +3743,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" hidden="1" spans="1:14">
+    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
         <v>71</v>
       </c>
@@ -4393,7 +3787,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" hidden="1" spans="1:14">
+    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
         <v>72</v>
       </c>
@@ -4437,7 +3831,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" hidden="1" spans="1:14">
+    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
         <v>73</v>
       </c>
@@ -4481,7 +3875,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" hidden="1" spans="1:14">
+    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
         <v>74</v>
       </c>
@@ -4525,7 +3919,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" hidden="1" spans="1:14">
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
         <v>76</v>
       </c>
@@ -4569,7 +3963,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" hidden="1" spans="1:14">
+    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
         <v>78</v>
       </c>
@@ -4613,7 +4007,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
         <v>79</v>
       </c>
@@ -4660,7 +4054,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" hidden="1" spans="1:14">
+    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
         <v>86</v>
       </c>
@@ -4704,7 +4098,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" hidden="1" spans="1:14">
+    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
         <v>87</v>
       </c>
@@ -4748,7 +4142,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" hidden="1" spans="1:14">
+    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
         <v>88</v>
       </c>
@@ -4792,7 +4186,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" hidden="1" spans="1:14">
+    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
         <v>89</v>
       </c>
@@ -4836,7 +4230,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" hidden="1" spans="1:14">
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
         <v>90</v>
       </c>
@@ -4880,7 +4274,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" hidden="1" spans="1:14">
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
         <v>91</v>
       </c>
@@ -4924,7 +4318,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" hidden="1" spans="1:14">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
         <v>92</v>
       </c>
@@ -4968,7 +4362,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" hidden="1" spans="1:14">
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
         <v>94</v>
       </c>
@@ -5012,7 +4406,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" hidden="1" spans="1:14">
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
         <v>95</v>
       </c>
@@ -5056,7 +4450,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:15">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
         <v>96</v>
       </c>
@@ -5103,7 +4497,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:15">
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
         <v>102</v>
       </c>
@@ -5150,7 +4544,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="41" hidden="1" spans="1:14">
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
         <v>112</v>
       </c>
@@ -5194,7 +4588,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" hidden="1" spans="1:14">
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
         <v>113</v>
       </c>
@@ -5238,7 +4632,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" hidden="1" spans="1:14">
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
         <v>114</v>
       </c>
@@ -5282,7 +4676,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" hidden="1" spans="1:14">
+    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
         <v>116</v>
       </c>
@@ -5326,7 +4720,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="1:14">
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
         <v>117</v>
       </c>
@@ -5370,7 +4764,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" hidden="1" spans="1:14">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
         <v>118</v>
       </c>
@@ -5414,7 +4808,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" hidden="1" spans="1:14">
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
         <v>119</v>
       </c>
@@ -5458,7 +4852,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" hidden="1" spans="1:14">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
         <v>120</v>
       </c>
@@ -5502,7 +4896,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" hidden="1" spans="1:14">
+    <row r="49" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
         <v>121</v>
       </c>
@@ -5546,7 +4940,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" hidden="1" spans="1:14">
+    <row r="50" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
         <v>122</v>
       </c>
@@ -5590,7 +4984,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" hidden="1" spans="1:14">
+    <row r="51" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
         <v>123</v>
       </c>
@@ -5634,7 +5028,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" hidden="1" spans="1:14">
+    <row r="52" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
         <v>124</v>
       </c>
@@ -5678,7 +5072,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" hidden="1" spans="1:14">
+    <row r="53" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
         <v>126</v>
       </c>
@@ -5722,7 +5116,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="54" hidden="1" spans="1:14">
+    <row r="54" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
         <v>127</v>
       </c>
@@ -5766,7 +5160,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" hidden="1" spans="1:14">
+    <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
         <v>128</v>
       </c>
@@ -5810,7 +5204,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="56" hidden="1" spans="1:14">
+    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
         <v>129</v>
       </c>
@@ -5854,7 +5248,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="57" hidden="1" spans="1:14">
+    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
         <v>130</v>
       </c>
@@ -5898,7 +5292,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="58" hidden="1" spans="1:14">
+    <row r="58" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
         <v>131</v>
       </c>
@@ -5942,7 +5336,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59" hidden="1" spans="1:14">
+    <row r="59" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
         <v>132</v>
       </c>
@@ -5986,7 +5380,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60" hidden="1" spans="1:14">
+    <row r="60" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
         <v>133</v>
       </c>
@@ -6030,7 +5424,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" hidden="1" spans="1:14">
+    <row r="61" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
         <v>134</v>
       </c>
@@ -6074,7 +5468,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" hidden="1" spans="1:14">
+    <row r="62" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
         <v>135</v>
       </c>
@@ -6118,7 +5512,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" hidden="1" spans="1:14">
+    <row r="63" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
         <v>136</v>
       </c>
@@ -6162,7 +5556,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" hidden="1" spans="1:14">
+    <row r="64" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
         <v>137</v>
       </c>
@@ -6206,7 +5600,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" hidden="1" spans="1:14">
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
         <v>138</v>
       </c>
@@ -6250,7 +5644,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:15">
+    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
         <v>139</v>
       </c>
@@ -6295,7 +5689,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="67" hidden="1" spans="1:14">
+    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
         <v>143</v>
       </c>
@@ -6339,7 +5733,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:15">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
         <v>144</v>
       </c>
@@ -6386,7 +5780,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="69" spans="1:15">
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
         <v>150</v>
       </c>
@@ -6433,7 +5827,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="70" hidden="1" spans="1:14">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
         <v>159</v>
       </c>
@@ -6477,7 +5871,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" hidden="1" spans="1:14">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
         <v>160</v>
       </c>
@@ -6521,7 +5915,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" hidden="1" spans="1:14">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
         <v>161</v>
       </c>
@@ -6565,7 +5959,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" hidden="1" spans="1:14">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
         <v>162</v>
       </c>
@@ -6609,7 +6003,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" hidden="1" spans="1:14">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
         <v>163</v>
       </c>
@@ -6653,7 +6047,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="75" hidden="1" spans="1:14">
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
         <v>164</v>
       </c>
@@ -6697,7 +6091,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="76" hidden="1" spans="1:14">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
         <v>165</v>
       </c>
@@ -6741,7 +6135,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="77" hidden="1" spans="1:14">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
         <v>167</v>
       </c>
@@ -6785,7 +6179,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="78" hidden="1" spans="1:14">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
         <v>168</v>
       </c>
@@ -6829,7 +6223,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="79" hidden="1" spans="1:14">
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
         <v>169</v>
       </c>
@@ -6873,7 +6267,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="80" hidden="1" spans="1:14">
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
         <v>170</v>
       </c>
@@ -6917,7 +6311,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" hidden="1" spans="1:14">
+    <row r="81" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
         <v>171</v>
       </c>
@@ -6961,7 +6355,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" hidden="1" spans="1:14">
+    <row r="82" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
         <v>172</v>
       </c>
@@ -7005,7 +6399,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" hidden="1" spans="1:14">
+    <row r="83" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
         <v>173</v>
       </c>
@@ -7049,7 +6443,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84" hidden="1" spans="1:14">
+    <row r="84" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
         <v>175</v>
       </c>
@@ -7093,7 +6487,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" hidden="1" spans="1:14">
+    <row r="85" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
         <v>176</v>
       </c>
@@ -7137,7 +6531,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="86" hidden="1" spans="1:14">
+    <row r="86" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
         <v>177</v>
       </c>
@@ -7181,7 +6575,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" hidden="1" spans="1:14">
+    <row r="87" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
         <v>178</v>
       </c>
@@ -7225,7 +6619,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="88" hidden="1" spans="1:14">
+    <row r="88" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
         <v>179</v>
       </c>
@@ -7269,7 +6663,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="89" hidden="1" spans="1:14">
+    <row r="89" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
         <v>180</v>
       </c>
@@ -7313,7 +6707,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" hidden="1" spans="1:14">
+    <row r="90" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
         <v>181</v>
       </c>
@@ -7357,7 +6751,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="91" hidden="1" spans="1:14">
+    <row r="91" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A91" s="2" t="s">
         <v>182</v>
       </c>
@@ -7401,7 +6795,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="92" hidden="1" spans="1:14">
+    <row r="92" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
         <v>183</v>
       </c>
@@ -7445,7 +6839,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="93" hidden="1" spans="1:14">
+    <row r="93" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A93" s="2" t="s">
         <v>184</v>
       </c>
@@ -7489,7 +6883,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="94" hidden="1" spans="1:14">
+    <row r="94" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A94" s="2" t="s">
         <v>185</v>
       </c>
@@ -7533,7 +6927,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="95" hidden="1" spans="1:14">
+    <row r="95" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A95" s="2" t="s">
         <v>186</v>
       </c>
@@ -7577,7 +6971,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="96" hidden="1" spans="1:14">
+    <row r="96" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A96" s="2" t="s">
         <v>187</v>
       </c>
@@ -7621,7 +7015,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="97" hidden="1" spans="1:14">
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A97" s="2" t="s">
         <v>188</v>
       </c>
@@ -7665,7 +7059,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="98" hidden="1" spans="1:14">
+    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A98" s="2" t="s">
         <v>189</v>
       </c>
@@ -7709,7 +7103,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="99" hidden="1" spans="1:14">
+    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A99" s="2" t="s">
         <v>190</v>
       </c>
@@ -7753,7 +7147,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="100" spans="1:15">
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A100" s="2" t="s">
         <v>191</v>
       </c>
@@ -7800,7 +7194,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="101" spans="1:15">
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A101" s="2" t="s">
         <v>192</v>
       </c>
@@ -7847,7 +7241,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="102" spans="1:15">
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A102" s="2" t="s">
         <v>193</v>
       </c>
@@ -7894,7 +7288,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="103" hidden="1" spans="1:14">
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A103" s="2" t="s">
         <v>194</v>
       </c>
@@ -7938,7 +7332,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="104" spans="1:15">
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A104" s="2" t="s">
         <v>196</v>
       </c>
@@ -7985,7 +7379,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="105" hidden="1" spans="1:14">
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A105" s="2" t="s">
         <v>198</v>
       </c>
@@ -8029,7 +7423,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="106" hidden="1" spans="1:14">
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A106" s="2" t="s">
         <v>199</v>
       </c>
@@ -8073,7 +7467,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="107" spans="1:15">
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A107" s="2" t="s">
         <v>200</v>
       </c>
@@ -8120,7 +7514,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="108" hidden="1" spans="1:14">
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A108" s="2" t="s">
         <v>207</v>
       </c>
@@ -8164,7 +7558,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="109" hidden="1" spans="1:14">
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A109" s="2" t="s">
         <v>208</v>
       </c>
@@ -8208,7 +7602,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="110" hidden="1" spans="1:14">
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A110" s="2" t="s">
         <v>209</v>
       </c>
@@ -8252,7 +7646,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="111" hidden="1" spans="1:14">
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A111" s="2" t="s">
         <v>210</v>
       </c>
@@ -8296,7 +7690,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="112" hidden="1" spans="1:14">
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A112" s="2" t="s">
         <v>211</v>
       </c>
@@ -8340,7 +7734,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="113" hidden="1" spans="1:14">
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A113" s="2" t="s">
         <v>212</v>
       </c>
@@ -8384,7 +7778,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="114" hidden="1" spans="1:14">
+    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A114" s="2" t="s">
         <v>213</v>
       </c>
@@ -8428,7 +7822,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="115" hidden="1" spans="1:14">
+    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A115" s="2" t="s">
         <v>214</v>
       </c>
@@ -8472,7 +7866,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="116" hidden="1" spans="1:14">
+    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A116" s="2" t="s">
         <v>215</v>
       </c>
@@ -8516,7 +7910,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="117" hidden="1" spans="1:14">
+    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A117" s="2" t="s">
         <v>216</v>
       </c>
@@ -8560,7 +7954,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="118" hidden="1" spans="1:14">
+    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A118" s="2" t="s">
         <v>217</v>
       </c>
@@ -8604,7 +7998,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="119" hidden="1" spans="1:14">
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A119" s="2" t="s">
         <v>218</v>
       </c>
@@ -8648,7 +8042,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="120" hidden="1" spans="1:14">
+    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A120" s="2" t="s">
         <v>219</v>
       </c>
@@ -8692,7 +8086,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="121" hidden="1" spans="1:14">
+    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A121" s="2" t="s">
         <v>220</v>
       </c>
@@ -8736,7 +8130,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="122" hidden="1" spans="1:14">
+    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A122" s="2" t="s">
         <v>221</v>
       </c>
@@ -8780,7 +8174,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="123" hidden="1" spans="1:14">
+    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A123" s="2" t="s">
         <v>222</v>
       </c>
@@ -8824,7 +8218,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="124" hidden="1" spans="1:14">
+    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A124" s="2" t="s">
         <v>223</v>
       </c>
@@ -8868,7 +8262,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="125" hidden="1" spans="1:14">
+    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A125" s="2" t="s">
         <v>224</v>
       </c>
@@ -8912,7 +8306,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="126" spans="1:15">
+    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A126" s="2" t="s">
         <v>225</v>
       </c>
@@ -8959,7 +8353,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="127" hidden="1" spans="1:14">
+    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A127" s="2" t="s">
         <v>231</v>
       </c>
@@ -9003,7 +8397,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="128" hidden="1" spans="1:14">
+    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A128" s="2" t="s">
         <v>232</v>
       </c>
@@ -9047,7 +8441,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="129" hidden="1" spans="1:14">
+    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A129" s="2" t="s">
         <v>233</v>
       </c>
@@ -9091,7 +8485,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="130" hidden="1" spans="1:14">
+    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A130" s="2" t="s">
         <v>234</v>
       </c>
@@ -9135,7 +8529,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="131" hidden="1" spans="1:14">
+    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A131" s="2" t="s">
         <v>235</v>
       </c>
@@ -9179,7 +8573,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="132" hidden="1" spans="1:14">
+    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A132" s="2" t="s">
         <v>236</v>
       </c>
@@ -9223,7 +8617,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="133" hidden="1" spans="1:14">
+    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A133" s="2" t="s">
         <v>237</v>
       </c>
@@ -9267,7 +8661,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="134" hidden="1" spans="1:14">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A134" s="2" t="s">
         <v>238</v>
       </c>
@@ -9311,7 +8705,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="135" hidden="1" spans="1:14">
+    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A135" s="2" t="s">
         <v>239</v>
       </c>
@@ -9355,7 +8749,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="136" hidden="1" spans="1:14">
+    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A136" s="2" t="s">
         <v>240</v>
       </c>
@@ -9399,7 +8793,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="137" hidden="1" spans="1:14">
+    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A137" s="2" t="s">
         <v>241</v>
       </c>
@@ -9443,7 +8837,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="138" hidden="1" spans="1:14">
+    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A138" s="2" t="s">
         <v>242</v>
       </c>
@@ -9487,7 +8881,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="139" spans="1:15">
+    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A139" s="2" t="s">
         <v>243</v>
       </c>
@@ -9534,7 +8928,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="140" hidden="1" spans="1:14">
+    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A140" s="2" t="s">
         <v>244</v>
       </c>
@@ -9578,7 +8972,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="141" spans="1:15">
+    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A141" s="2" t="s">
         <v>245</v>
       </c>
@@ -9625,7 +9019,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="142" hidden="1" spans="1:14">
+    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A142" s="2" t="s">
         <v>248</v>
       </c>
@@ -9669,7 +9063,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="143" hidden="1" spans="1:14">
+    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A143" s="2" t="s">
         <v>249</v>
       </c>
@@ -9713,7 +9107,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="144" hidden="1" spans="1:14">
+    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A144" s="2" t="s">
         <v>250</v>
       </c>
@@ -9757,7 +9151,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="145" hidden="1" spans="1:14">
+    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A145" s="2" t="s">
         <v>251</v>
       </c>
@@ -9801,7 +9195,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="146" hidden="1" spans="1:14">
+    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A146" s="2" t="s">
         <v>252</v>
       </c>
@@ -9845,7 +9239,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="147" spans="1:15">
+    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A147" s="2" t="s">
         <v>253</v>
       </c>
@@ -9892,7 +9286,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="148" spans="1:15">
+    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A148" s="2" t="s">
         <v>255</v>
       </c>
@@ -9939,7 +9333,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="149" hidden="1" spans="1:14">
+    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A149" s="2" t="s">
         <v>256</v>
       </c>
@@ -9983,7 +9377,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="150" hidden="1" spans="1:14">
+    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A150" s="2" t="s">
         <v>258</v>
       </c>
@@ -10027,7 +9421,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="151" hidden="1" spans="1:14">
+    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A151" s="2" t="s">
         <v>260</v>
       </c>
@@ -10071,7 +9465,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="152" hidden="1" spans="1:14">
+    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A152" s="2" t="s">
         <v>261</v>
       </c>
@@ -10115,7 +9509,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="153" hidden="1" spans="1:14">
+    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A153" s="2" t="s">
         <v>262</v>
       </c>
@@ -10159,7 +9553,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="154" hidden="1" spans="1:14">
+    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A154" s="2" t="s">
         <v>263</v>
       </c>
@@ -10203,7 +9597,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="155" hidden="1" spans="1:14">
+    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A155" s="2" t="s">
         <v>264</v>
       </c>
@@ -10247,7 +9641,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="156" hidden="1" spans="1:14">
+    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A156" s="2" t="s">
         <v>265</v>
       </c>
@@ -10291,7 +9685,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="157" hidden="1" spans="1:14">
+    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A157" s="2" t="s">
         <v>266</v>
       </c>
@@ -10335,7 +9729,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="158" hidden="1" spans="1:14">
+    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A158" s="2" t="s">
         <v>267</v>
       </c>
@@ -10379,7 +9773,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="159" hidden="1" spans="1:14">
+    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A159" s="2" t="s">
         <v>268</v>
       </c>
@@ -10423,7 +9817,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="160" spans="1:15">
+    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A160" s="2" t="s">
         <v>269</v>
       </c>
@@ -10470,7 +9864,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="161" spans="1:15">
+    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A161" s="2" t="s">
         <v>270</v>
       </c>
@@ -10517,7 +9911,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="162" hidden="1" spans="1:14">
+    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A162" s="2" t="s">
         <v>271</v>
       </c>
@@ -10561,7 +9955,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="163" hidden="1" spans="1:14">
+    <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A163" s="2" t="s">
         <v>272</v>
       </c>
@@ -10605,7 +9999,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="164" hidden="1" spans="1:14">
+    <row r="164" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A164" s="2" t="s">
         <v>273</v>
       </c>
@@ -10649,7 +10043,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="165" hidden="1" spans="1:14">
+    <row r="165" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A165" s="2" t="s">
         <v>274</v>
       </c>
@@ -10693,7 +10087,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="166" hidden="1" spans="1:14">
+    <row r="166" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A166" s="2" t="s">
         <v>275</v>
       </c>
@@ -10737,7 +10131,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="167" hidden="1" spans="1:14">
+    <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A167" s="2" t="s">
         <v>276</v>
       </c>
@@ -10781,7 +10175,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="168" hidden="1" spans="1:14">
+    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A168" s="2" t="s">
         <v>277</v>
       </c>
@@ -10825,7 +10219,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="169" hidden="1" spans="1:14">
+    <row r="169" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A169" s="2" t="s">
         <v>278</v>
       </c>
@@ -10869,7 +10263,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="170" hidden="1" spans="1:14">
+    <row r="170" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A170" s="2" t="s">
         <v>279</v>
       </c>
@@ -10913,7 +10307,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="171" hidden="1" spans="1:14">
+    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A171" s="2" t="s">
         <v>280</v>
       </c>
@@ -10957,7 +10351,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="172" hidden="1" spans="1:14">
+    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A172" s="2" t="s">
         <v>281</v>
       </c>
@@ -11001,7 +10395,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="173" hidden="1" spans="1:14">
+    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A173" s="2" t="s">
         <v>282</v>
       </c>
@@ -11045,7 +10439,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="174" hidden="1" spans="1:14">
+    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A174" s="2" t="s">
         <v>283</v>
       </c>
@@ -11089,7 +10483,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="175" hidden="1" spans="1:14">
+    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A175" s="2" t="s">
         <v>284</v>
       </c>
@@ -11133,7 +10527,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="176" hidden="1" spans="1:14">
+    <row r="176" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A176" s="2" t="s">
         <v>285</v>
       </c>
@@ -11177,7 +10571,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="177" hidden="1" spans="1:14">
+    <row r="177" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A177" s="2" t="s">
         <v>286</v>
       </c>
@@ -11221,7 +10615,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="178" hidden="1" spans="1:14">
+    <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A178" s="2" t="s">
         <v>287</v>
       </c>
@@ -11265,7 +10659,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="179" hidden="1" spans="1:14">
+    <row r="179" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A179" s="2" t="s">
         <v>288</v>
       </c>
@@ -11309,7 +10703,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="180" hidden="1" spans="1:14">
+    <row r="180" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A180" s="2" t="s">
         <v>289</v>
       </c>
@@ -11353,7 +10747,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="181" hidden="1" spans="1:14">
+    <row r="181" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A181" s="2" t="s">
         <v>290</v>
       </c>
@@ -11397,7 +10791,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="182" hidden="1" spans="1:14">
+    <row r="182" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A182" s="2" t="s">
         <v>291</v>
       </c>
@@ -11441,7 +10835,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="183" spans="1:15">
+    <row r="183" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A183" s="2" t="s">
         <v>292</v>
       </c>
@@ -11488,7 +10882,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="184" spans="1:15">
+    <row r="184" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A184" s="2" t="s">
         <v>296</v>
       </c>
@@ -11535,7 +10929,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="185" spans="1:15">
+    <row r="185" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A185" s="2" t="s">
         <v>300</v>
       </c>
@@ -11582,7 +10976,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="186" spans="1:15">
+    <row r="186" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A186" s="2" t="s">
         <v>303</v>
       </c>
@@ -11629,7 +11023,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="187" spans="1:15">
+    <row r="187" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A187" s="2" t="s">
         <v>304</v>
       </c>
@@ -11676,7 +11070,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="188" spans="1:15">
+    <row r="188" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A188" s="2" t="s">
         <v>305</v>
       </c>
@@ -11723,7 +11117,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="189" spans="1:15">
+    <row r="189" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A189" s="2" t="s">
         <v>306</v>
       </c>
@@ -11770,7 +11164,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="190" spans="1:15">
+    <row r="190" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A190" s="2" t="s">
         <v>307</v>
       </c>
@@ -11817,7 +11211,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="191" spans="1:15">
+    <row r="191" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A191" s="2" t="s">
         <v>308</v>
       </c>
@@ -11864,7 +11258,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="192" spans="1:15">
+    <row r="192" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A192" s="2" t="s">
         <v>309</v>
       </c>
@@ -11911,7 +11305,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="193" spans="1:15">
+    <row r="193" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A193" s="2" t="s">
         <v>310</v>
       </c>
@@ -11958,7 +11352,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="194" spans="1:15">
+    <row r="194" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A194" s="2" t="s">
         <v>311</v>
       </c>
@@ -12005,7 +11399,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="195" spans="1:15">
+    <row r="195" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A195" s="2" t="s">
         <v>312</v>
       </c>
@@ -12052,7 +11446,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="196" spans="1:15">
+    <row r="196" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A196" s="2" t="s">
         <v>313</v>
       </c>
@@ -12099,7 +11493,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="197" spans="1:15">
+    <row r="197" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A197" s="2" t="s">
         <v>314</v>
       </c>
@@ -12146,7 +11540,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="198" spans="1:15">
+    <row r="198" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A198" s="2" t="s">
         <v>315</v>
       </c>
@@ -12193,7 +11587,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="199" spans="1:15">
+    <row r="199" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A199" s="2" t="s">
         <v>316</v>
       </c>
@@ -12240,7 +11634,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="200" spans="1:15">
+    <row r="200" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A200" s="2" t="s">
         <v>317</v>
       </c>
@@ -12287,7 +11681,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="201" spans="1:15">
+    <row r="201" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A201" s="2" t="s">
         <v>318</v>
       </c>
@@ -12334,7 +11728,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="202" spans="1:15">
+    <row r="202" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A202" s="2" t="s">
         <v>319</v>
       </c>
@@ -12381,7 +11775,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="203" spans="1:15">
+    <row r="203" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A203" s="2" t="s">
         <v>320</v>
       </c>
@@ -12428,7 +11822,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="204" spans="1:15">
+    <row r="204" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A204" s="2" t="s">
         <v>321</v>
       </c>
@@ -12475,7 +11869,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="205" spans="1:15">
+    <row r="205" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A205" s="2" t="s">
         <v>322</v>
       </c>
@@ -12522,7 +11916,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="206" spans="1:15">
+    <row r="206" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A206" s="2" t="s">
         <v>323</v>
       </c>
@@ -12569,7 +11963,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="207" spans="1:15">
+    <row r="207" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A207" s="2" t="s">
         <v>324</v>
       </c>
@@ -12616,7 +12010,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="208" spans="1:15">
+    <row r="208" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A208" s="2" t="s">
         <v>325</v>
       </c>
@@ -12663,7 +12057,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="209" spans="1:15">
+    <row r="209" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A209" s="2" t="s">
         <v>326</v>
       </c>
@@ -12710,7 +12104,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="210" spans="1:15">
+    <row r="210" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A210" s="2" t="s">
         <v>327</v>
       </c>
@@ -12757,7 +12151,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="211" spans="1:15">
+    <row r="211" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A211" s="2" t="s">
         <v>328</v>
       </c>
@@ -12804,7 +12198,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="212" spans="1:15">
+    <row r="212" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A212" s="2" t="s">
         <v>329</v>
       </c>
@@ -12851,7 +12245,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="213" spans="1:15">
+    <row r="213" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A213" s="2" t="s">
         <v>330</v>
       </c>
@@ -12898,7 +12292,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="214" spans="1:15">
+    <row r="214" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A214" s="2" t="s">
         <v>331</v>
       </c>
@@ -12945,7 +12339,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="215" spans="1:15">
+    <row r="215" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A215" s="2" t="s">
         <v>332</v>
       </c>
@@ -12992,7 +12386,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="216" spans="1:15">
+    <row r="216" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A216" s="2" t="s">
         <v>333</v>
       </c>
@@ -13039,7 +12433,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="217" spans="1:15">
+    <row r="217" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A217" s="2" t="s">
         <v>334</v>
       </c>
@@ -13086,7 +12480,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="218" spans="1:15">
+    <row r="218" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A218" s="2" t="s">
         <v>335</v>
       </c>
@@ -13133,7 +12527,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="219" spans="1:15">
+    <row r="219" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A219" s="2" t="s">
         <v>336</v>
       </c>
@@ -13180,7 +12574,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="220" spans="1:15">
+    <row r="220" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A220" s="2" t="s">
         <v>337</v>
       </c>
@@ -13227,7 +12621,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="221" spans="1:15">
+    <row r="221" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A221" s="2" t="s">
         <v>343</v>
       </c>
@@ -13274,7 +12668,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="222" spans="1:15">
+    <row r="222" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A222" s="2" t="s">
         <v>344</v>
       </c>
@@ -13321,7 +12715,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="223" spans="1:15">
+    <row r="223" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A223" s="2" t="s">
         <v>348</v>
       </c>
@@ -13368,7 +12762,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="224" spans="1:15">
+    <row r="224" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A224" s="2" t="s">
         <v>353</v>
       </c>
@@ -13415,7 +12809,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="225" spans="1:15">
+    <row r="225" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A225" s="2" t="s">
         <v>355</v>
       </c>
@@ -13462,7 +12856,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="226" spans="1:15">
+    <row r="226" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A226" s="2" t="s">
         <v>359</v>
       </c>
@@ -13509,7 +12903,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="227" spans="1:15">
+    <row r="227" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A227" s="2" t="s">
         <v>360</v>
       </c>
@@ -13556,7 +12950,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="228" spans="1:15">
+    <row r="228" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A228" s="2" t="s">
         <v>363</v>
       </c>
@@ -13603,7 +12997,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="229" spans="1:15">
+    <row r="229" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A229" s="2" t="s">
         <v>364</v>
       </c>
@@ -13650,7 +13044,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="230" spans="1:15">
+    <row r="230" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A230" s="2" t="s">
         <v>366</v>
       </c>
@@ -13697,7 +13091,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="231" spans="1:15">
+    <row r="231" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A231" s="2" t="s">
         <v>369</v>
       </c>
@@ -13744,7 +13138,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="232" spans="1:15">
+    <row r="232" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A232" s="2" t="s">
         <v>370</v>
       </c>
@@ -13791,7 +13185,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="233" spans="1:15">
+    <row r="233" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A233" s="2" t="s">
         <v>373</v>
       </c>
@@ -13838,7 +13232,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="234" hidden="1" spans="1:14">
+    <row r="234" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A234" s="2" t="s">
         <v>376</v>
       </c>
@@ -13882,7 +13276,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="235" hidden="1" spans="1:14">
+    <row r="235" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A235" s="2" t="s">
         <v>377</v>
       </c>
@@ -13926,7 +13320,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="236" hidden="1" spans="1:14">
+    <row r="236" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A236" s="2" t="s">
         <v>378</v>
       </c>
@@ -13970,7 +13364,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="237" hidden="1" spans="1:14">
+    <row r="237" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A237" s="2" t="s">
         <v>379</v>
       </c>
@@ -14014,7 +13408,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="238" hidden="1" spans="1:14">
+    <row r="238" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A238" s="2" t="s">
         <v>380</v>
       </c>
@@ -14058,7 +13452,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="239" hidden="1" spans="1:14">
+    <row r="239" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A239" s="2" t="s">
         <v>381</v>
       </c>
@@ -14102,7 +13496,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="240" hidden="1" spans="1:14">
+    <row r="240" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A240" s="2" t="s">
         <v>382</v>
       </c>
@@ -14146,7 +13540,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="241" hidden="1" spans="1:14">
+    <row r="241" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A241" s="2" t="s">
         <v>383</v>
       </c>
@@ -14190,7 +13584,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="242" hidden="1" spans="1:14">
+    <row r="242" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A242" s="2" t="s">
         <v>384</v>
       </c>
@@ -14234,7 +13628,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="243" hidden="1" spans="1:14">
+    <row r="243" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A243" s="2" t="s">
         <v>385</v>
       </c>
@@ -14278,7 +13672,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="244" hidden="1" spans="1:14">
+    <row r="244" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A244" s="2" t="s">
         <v>386</v>
       </c>
@@ -14322,7 +13716,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="245" hidden="1" spans="1:14">
+    <row r="245" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A245" s="2" t="s">
         <v>387</v>
       </c>
@@ -14366,7 +13760,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="246" hidden="1" spans="1:14">
+    <row r="246" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A246" s="2" t="s">
         <v>388</v>
       </c>
@@ -14410,7 +13804,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="247" hidden="1" spans="1:14">
+    <row r="247" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A247" s="2" t="s">
         <v>389</v>
       </c>
@@ -14454,7 +13848,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="248" hidden="1" spans="1:14">
+    <row r="248" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A248" s="2" t="s">
         <v>390</v>
       </c>
@@ -14498,7 +13892,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="249" hidden="1" spans="1:14">
+    <row r="249" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A249" s="2" t="s">
         <v>391</v>
       </c>
@@ -14542,7 +13936,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="250" hidden="1" spans="1:14">
+    <row r="250" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A250" s="2" t="s">
         <v>392</v>
       </c>
@@ -14586,7 +13980,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="251" hidden="1" spans="1:14">
+    <row r="251" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A251" s="2" t="s">
         <v>393</v>
       </c>
@@ -14630,7 +14024,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="252" hidden="1" spans="1:14">
+    <row r="252" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A252" s="2" t="s">
         <v>394</v>
       </c>
@@ -14674,7 +14068,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="253" hidden="1" spans="1:14">
+    <row r="253" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A253" s="2" t="s">
         <v>395</v>
       </c>
@@ -14718,7 +14112,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="254" hidden="1" spans="1:14">
+    <row r="254" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A254" s="2" t="s">
         <v>396</v>
       </c>
@@ -14762,7 +14156,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="255" hidden="1" spans="1:14">
+    <row r="255" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A255" s="2" t="s">
         <v>397</v>
       </c>
@@ -14806,7 +14200,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="256" hidden="1" spans="1:14">
+    <row r="256" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A256" s="2" t="s">
         <v>398</v>
       </c>
@@ -14850,7 +14244,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="257" hidden="1" spans="1:14">
+    <row r="257" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A257" s="2" t="s">
         <v>399</v>
       </c>
@@ -14894,7 +14288,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="258" hidden="1" spans="1:14">
+    <row r="258" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A258" s="2" t="s">
         <v>400</v>
       </c>
@@ -14938,7 +14332,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="259" hidden="1" spans="1:14">
+    <row r="259" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A259" s="2" t="s">
         <v>401</v>
       </c>
@@ -14982,7 +14376,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="260" hidden="1" spans="1:14">
+    <row r="260" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A260" s="2" t="s">
         <v>402</v>
       </c>
@@ -15026,7 +14420,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="261" hidden="1" spans="1:14">
+    <row r="261" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A261" s="2" t="s">
         <v>403</v>
       </c>
@@ -15070,7 +14464,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="262" hidden="1" spans="1:14">
+    <row r="262" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A262" s="2" t="s">
         <v>404</v>
       </c>
@@ -15114,7 +14508,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="263" hidden="1" spans="1:14">
+    <row r="263" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A263" s="2" t="s">
         <v>405</v>
       </c>
@@ -15158,7 +14552,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="264" hidden="1" spans="1:14">
+    <row r="264" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A264" s="2" t="s">
         <v>406</v>
       </c>
@@ -15202,7 +14596,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="265" hidden="1" spans="1:14">
+    <row r="265" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A265" s="2" t="s">
         <v>407</v>
       </c>
@@ -15246,7 +14640,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="266" hidden="1" spans="1:14">
+    <row r="266" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A266" s="2" t="s">
         <v>408</v>
       </c>
@@ -15290,7 +14684,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="267" hidden="1" spans="1:14">
+    <row r="267" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A267" s="2" t="s">
         <v>409</v>
       </c>
@@ -15334,7 +14728,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="268" hidden="1" spans="1:14">
+    <row r="268" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A268" s="2" t="s">
         <v>410</v>
       </c>
@@ -15378,7 +14772,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="269" hidden="1" spans="1:14">
+    <row r="269" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A269" s="2" t="s">
         <v>411</v>
       </c>
@@ -15422,7 +14816,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="270" hidden="1" spans="1:14">
+    <row r="270" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A270" s="2" t="s">
         <v>412</v>
       </c>
@@ -15466,7 +14860,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="271" hidden="1" spans="1:14">
+    <row r="271" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A271" s="2" t="s">
         <v>413</v>
       </c>
@@ -15510,7 +14904,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="272" hidden="1" spans="1:14">
+    <row r="272" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A272" s="2" t="s">
         <v>414</v>
       </c>
@@ -15554,7 +14948,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="273" hidden="1" spans="1:14">
+    <row r="273" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A273" s="2" t="s">
         <v>415</v>
       </c>
@@ -15598,7 +14992,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="274" hidden="1" spans="1:14">
+    <row r="274" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A274" s="2" t="s">
         <v>416</v>
       </c>
@@ -15642,7 +15036,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="275" hidden="1" spans="1:14">
+    <row r="275" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A275" s="2" t="s">
         <v>417</v>
       </c>
@@ -15686,7 +15080,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="276" hidden="1" spans="1:14">
+    <row r="276" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A276" s="2" t="s">
         <v>418</v>
       </c>
@@ -15730,7 +15124,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="277" hidden="1" spans="1:14">
+    <row r="277" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A277" s="2" t="s">
         <v>419</v>
       </c>
@@ -15774,7 +15168,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="278" hidden="1" spans="1:14">
+    <row r="278" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A278" s="2" t="s">
         <v>420</v>
       </c>
@@ -15818,7 +15212,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="279" hidden="1" spans="1:14">
+    <row r="279" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A279" s="2" t="s">
         <v>421</v>
       </c>
@@ -15862,7 +15256,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="280" hidden="1" spans="1:14">
+    <row r="280" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A280" s="2" t="s">
         <v>422</v>
       </c>
@@ -15906,7 +15300,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="281" hidden="1" spans="1:14">
+    <row r="281" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A281" s="2" t="s">
         <v>423</v>
       </c>
@@ -15950,7 +15344,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="282" hidden="1" spans="1:14">
+    <row r="282" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A282" s="2" t="s">
         <v>424</v>
       </c>
@@ -15994,7 +15388,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="283" hidden="1" spans="1:14">
+    <row r="283" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A283" s="2" t="s">
         <v>425</v>
       </c>
@@ -16038,7 +15432,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="284" hidden="1" spans="1:14">
+    <row r="284" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A284" s="2" t="s">
         <v>426</v>
       </c>
@@ -16082,7 +15476,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="285" hidden="1" spans="1:14">
+    <row r="285" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A285" s="2" t="s">
         <v>427</v>
       </c>
@@ -16126,7 +15520,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="286" hidden="1" spans="1:14">
+    <row r="286" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A286" s="2" t="s">
         <v>428</v>
       </c>
@@ -16170,7 +15564,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="287" hidden="1" spans="1:14">
+    <row r="287" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A287" s="2" t="s">
         <v>429</v>
       </c>
@@ -16214,7 +15608,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="288" hidden="1" spans="1:14">
+    <row r="288" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A288" s="2" t="s">
         <v>430</v>
       </c>
@@ -16258,7 +15652,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="289" hidden="1" spans="1:14">
+    <row r="289" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A289" s="2" t="s">
         <v>431</v>
       </c>
@@ -16302,7 +15696,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="290" hidden="1" spans="1:14">
+    <row r="290" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A290" s="2" t="s">
         <v>432</v>
       </c>
@@ -16346,7 +15740,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="291" hidden="1" spans="1:14">
+    <row r="291" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A291" s="2" t="s">
         <v>433</v>
       </c>
@@ -16390,7 +15784,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="292" hidden="1" spans="1:14">
+    <row r="292" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A292" s="2" t="s">
         <v>434</v>
       </c>
@@ -16434,7 +15828,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="293" hidden="1" spans="1:14">
+    <row r="293" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A293" s="2" t="s">
         <v>435</v>
       </c>
@@ -16478,7 +15872,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="294" hidden="1" spans="1:14">
+    <row r="294" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A294" s="2" t="s">
         <v>436</v>
       </c>
@@ -16522,7 +15916,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="295" hidden="1" spans="1:14">
+    <row r="295" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A295" s="2" t="s">
         <v>437</v>
       </c>
@@ -16566,7 +15960,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="296" hidden="1" spans="1:14">
+    <row r="296" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A296" s="2" t="s">
         <v>438</v>
       </c>
@@ -16610,7 +16004,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="297" hidden="1" spans="1:14">
+    <row r="297" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A297" s="2" t="s">
         <v>439</v>
       </c>
@@ -16654,7 +16048,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="298" hidden="1" spans="1:14">
+    <row r="298" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A298" s="2" t="s">
         <v>440</v>
       </c>
@@ -16698,7 +16092,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="299" hidden="1" spans="1:14">
+    <row r="299" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A299" s="2" t="s">
         <v>441</v>
       </c>
@@ -16742,7 +16136,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="300" hidden="1" spans="1:14">
+    <row r="300" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A300" s="2" t="s">
         <v>442</v>
       </c>
@@ -16786,7 +16180,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="301" hidden="1" spans="1:14">
+    <row r="301" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A301" s="2" t="s">
         <v>443</v>
       </c>
@@ -16830,7 +16224,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="302" hidden="1" spans="1:14">
+    <row r="302" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A302" s="2" t="s">
         <v>444</v>
       </c>
@@ -16874,7 +16268,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="303" hidden="1" spans="1:14">
+    <row r="303" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A303" s="2" t="s">
         <v>445</v>
       </c>
@@ -16918,7 +16312,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="304" hidden="1" spans="1:14">
+    <row r="304" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A304" s="2" t="s">
         <v>446</v>
       </c>
@@ -16962,7 +16356,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="305" hidden="1" spans="1:14">
+    <row r="305" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A305" s="2" t="s">
         <v>447</v>
       </c>
@@ -17006,7 +16400,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="306" hidden="1" spans="1:14">
+    <row r="306" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A306" s="2" t="s">
         <v>448</v>
       </c>
@@ -17050,7 +16444,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="307" hidden="1" spans="1:14">
+    <row r="307" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A307" s="2" t="s">
         <v>449</v>
       </c>
@@ -17094,7 +16488,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="308" hidden="1" spans="1:14">
+    <row r="308" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A308" s="2" t="s">
         <v>450</v>
       </c>
@@ -17138,7 +16532,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="309" hidden="1" spans="1:14">
+    <row r="309" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A309" s="2" t="s">
         <v>451</v>
       </c>
@@ -17182,7 +16576,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="310" hidden="1" spans="1:14">
+    <row r="310" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A310" s="2" t="s">
         <v>452</v>
       </c>
@@ -17226,7 +16620,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="311" hidden="1" spans="1:14">
+    <row r="311" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A311" s="2" t="s">
         <v>453</v>
       </c>
@@ -17270,7 +16664,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="312" hidden="1" spans="1:14">
+    <row r="312" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A312" s="2" t="s">
         <v>454</v>
       </c>
@@ -17314,7 +16708,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="313" hidden="1" spans="1:14">
+    <row r="313" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A313" s="2" t="s">
         <v>455</v>
       </c>
@@ -17358,7 +16752,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="314" hidden="1" spans="1:14">
+    <row r="314" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A314" s="2" t="s">
         <v>456</v>
       </c>
@@ -17402,7 +16796,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="315" hidden="1" spans="1:14">
+    <row r="315" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A315" s="2" t="s">
         <v>457</v>
       </c>
@@ -17446,7 +16840,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="316" hidden="1" spans="1:14">
+    <row r="316" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A316" s="2" t="s">
         <v>458</v>
       </c>
@@ -17490,7 +16884,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="317" hidden="1" spans="1:14">
+    <row r="317" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A317" s="2" t="s">
         <v>459</v>
       </c>
@@ -17534,7 +16928,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="318" hidden="1" spans="1:14">
+    <row r="318" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A318" s="2" t="s">
         <v>460</v>
       </c>
@@ -17578,7 +16972,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="319" hidden="1" spans="1:14">
+    <row r="319" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A319" s="2" t="s">
         <v>461</v>
       </c>
@@ -17622,7 +17016,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="320" hidden="1" spans="1:14">
+    <row r="320" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A320" s="2" t="s">
         <v>462</v>
       </c>
@@ -17666,7 +17060,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="321" hidden="1" spans="1:14">
+    <row r="321" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A321" s="2" t="s">
         <v>463</v>
       </c>
@@ -17710,7 +17104,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="322" hidden="1" spans="1:14">
+    <row r="322" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A322" s="2" t="s">
         <v>464</v>
       </c>
@@ -17754,7 +17148,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="323" hidden="1" spans="1:14">
+    <row r="323" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A323" s="2" t="s">
         <v>465</v>
       </c>
@@ -17798,7 +17192,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="324" hidden="1" spans="1:14">
+    <row r="324" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A324" s="2" t="s">
         <v>466</v>
       </c>
@@ -17842,7 +17236,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="325" hidden="1" spans="1:14">
+    <row r="325" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A325" s="2" t="s">
         <v>467</v>
       </c>
@@ -17886,7 +17280,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="326" hidden="1" spans="1:14">
+    <row r="326" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A326" s="2" t="s">
         <v>468</v>
       </c>
@@ -17930,7 +17324,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="327" hidden="1" spans="1:14">
+    <row r="327" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A327" s="2" t="s">
         <v>469</v>
       </c>
@@ -17974,7 +17368,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="328" hidden="1" spans="1:14">
+    <row r="328" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A328" s="2" t="s">
         <v>470</v>
       </c>
@@ -18018,7 +17412,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="329" hidden="1" spans="1:14">
+    <row r="329" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A329" s="2" t="s">
         <v>471</v>
       </c>
@@ -18062,7 +17456,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="330" hidden="1" spans="1:14">
+    <row r="330" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A330" s="2" t="s">
         <v>472</v>
       </c>
@@ -18106,7 +17500,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="331" hidden="1" spans="1:14">
+    <row r="331" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A331" s="2" t="s">
         <v>473</v>
       </c>
@@ -18150,7 +17544,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="332" hidden="1" spans="1:14">
+    <row r="332" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A332" s="2" t="s">
         <v>474</v>
       </c>
@@ -18194,7 +17588,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="333" hidden="1" spans="1:14">
+    <row r="333" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A333" s="2" t="s">
         <v>475</v>
       </c>
@@ -18238,7 +17632,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="334" hidden="1" spans="1:14">
+    <row r="334" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A334" s="2" t="s">
         <v>476</v>
       </c>
@@ -18282,7 +17676,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="335" hidden="1" spans="1:14">
+    <row r="335" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A335" s="2" t="s">
         <v>477</v>
       </c>
@@ -18326,7 +17720,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="336" hidden="1" spans="1:14">
+    <row r="336" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A336" s="2" t="s">
         <v>478</v>
       </c>
@@ -18370,7 +17764,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="337" hidden="1" spans="1:14">
+    <row r="337" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A337" s="2" t="s">
         <v>479</v>
       </c>
@@ -18414,7 +17808,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="338" hidden="1" spans="1:14">
+    <row r="338" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A338" s="2" t="s">
         <v>480</v>
       </c>
@@ -18458,7 +17852,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="339" hidden="1" spans="1:14">
+    <row r="339" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A339" s="2" t="s">
         <v>481</v>
       </c>
@@ -18502,7 +17896,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="340" hidden="1" spans="1:14">
+    <row r="340" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A340" s="2" t="s">
         <v>482</v>
       </c>
@@ -18546,7 +17940,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="341" hidden="1" spans="1:14">
+    <row r="341" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A341" s="2" t="s">
         <v>483</v>
       </c>
@@ -18590,7 +17984,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="342" hidden="1" spans="1:14">
+    <row r="342" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A342" s="2" t="s">
         <v>484</v>
       </c>
@@ -18634,7 +18028,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="343" hidden="1" spans="1:14">
+    <row r="343" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A343" s="2" t="s">
         <v>485</v>
       </c>
@@ -18678,7 +18072,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="344" hidden="1" spans="1:14">
+    <row r="344" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A344" s="2" t="s">
         <v>486</v>
       </c>
@@ -18722,7 +18116,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="345" hidden="1" spans="1:14">
+    <row r="345" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A345" s="2" t="s">
         <v>487</v>
       </c>
@@ -18766,7 +18160,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="346" hidden="1" spans="1:14">
+    <row r="346" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A346" s="2" t="s">
         <v>488</v>
       </c>
@@ -18810,7 +18204,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="347" hidden="1" spans="1:14">
+    <row r="347" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A347" s="2" t="s">
         <v>489</v>
       </c>
@@ -18854,7 +18248,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="348" hidden="1" spans="1:14">
+    <row r="348" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A348" s="2" t="s">
         <v>490</v>
       </c>
@@ -18898,7 +18292,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="349" hidden="1" spans="1:14">
+    <row r="349" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A349" s="2" t="s">
         <v>491</v>
       </c>
@@ -18942,7 +18336,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="350" hidden="1" spans="1:14">
+    <row r="350" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A350" s="2" t="s">
         <v>492</v>
       </c>
@@ -18986,7 +18380,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="351" hidden="1" spans="1:14">
+    <row r="351" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A351" s="2" t="s">
         <v>493</v>
       </c>
@@ -19030,7 +18424,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="352" hidden="1" spans="1:14">
+    <row r="352" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A352" s="2" t="s">
         <v>494</v>
       </c>
@@ -19074,7 +18468,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="353" hidden="1" spans="1:14">
+    <row r="353" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A353" s="2" t="s">
         <v>495</v>
       </c>
@@ -19118,7 +18512,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="354" hidden="1" spans="1:14">
+    <row r="354" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A354" s="2" t="s">
         <v>496</v>
       </c>
@@ -19162,7 +18556,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="355" hidden="1" spans="1:14">
+    <row r="355" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A355" s="2" t="s">
         <v>497</v>
       </c>
@@ -19206,7 +18600,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="356" hidden="1" spans="1:14">
+    <row r="356" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A356" s="2" t="s">
         <v>498</v>
       </c>
@@ -19250,7 +18644,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="357" hidden="1" spans="1:14">
+    <row r="357" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A357" s="2" t="s">
         <v>499</v>
       </c>
@@ -19294,7 +18688,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="358" hidden="1" spans="1:14">
+    <row r="358" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A358" s="2" t="s">
         <v>500</v>
       </c>
@@ -19338,7 +18732,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="359" hidden="1" spans="1:14">
+    <row r="359" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A359" s="2" t="s">
         <v>501</v>
       </c>
@@ -19382,7 +18776,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="360" hidden="1" spans="1:14">
+    <row r="360" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A360" s="2" t="s">
         <v>502</v>
       </c>
@@ -19426,7 +18820,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="361" hidden="1" spans="1:14">
+    <row r="361" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A361" s="2" t="s">
         <v>503</v>
       </c>
@@ -19470,7 +18864,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="362" hidden="1" spans="1:14">
+    <row r="362" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A362" s="2" t="s">
         <v>504</v>
       </c>
@@ -19514,7 +18908,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="363" hidden="1" spans="1:14">
+    <row r="363" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A363" s="2" t="s">
         <v>505</v>
       </c>
@@ -19558,7 +18952,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="364" hidden="1" spans="1:14">
+    <row r="364" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A364" s="2" t="s">
         <v>506</v>
       </c>
@@ -19602,7 +18996,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="365" hidden="1" spans="1:14">
+    <row r="365" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A365" s="2" t="s">
         <v>507</v>
       </c>
@@ -19646,7 +19040,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="366" hidden="1" spans="1:14">
+    <row r="366" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A366" s="2" t="s">
         <v>508</v>
       </c>
@@ -19690,7 +19084,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="367" hidden="1" spans="1:14">
+    <row r="367" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A367" s="2" t="s">
         <v>509</v>
       </c>
@@ -19734,7 +19128,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="368" hidden="1" spans="1:14">
+    <row r="368" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A368" s="2" t="s">
         <v>510</v>
       </c>
@@ -19778,7 +19172,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="369" hidden="1" spans="1:14">
+    <row r="369" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A369" s="2" t="s">
         <v>511</v>
       </c>
@@ -19822,7 +19216,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="370" hidden="1" spans="1:14">
+    <row r="370" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A370" s="2" t="s">
         <v>512</v>
       </c>
@@ -19866,7 +19260,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="371" hidden="1" spans="1:14">
+    <row r="371" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A371" s="2" t="s">
         <v>513</v>
       </c>
@@ -19910,7 +19304,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="372" hidden="1" spans="1:14">
+    <row r="372" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A372" s="2" t="s">
         <v>514</v>
       </c>
@@ -19954,7 +19348,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="373" hidden="1" spans="1:14">
+    <row r="373" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A373" s="2" t="s">
         <v>515</v>
       </c>
@@ -19998,7 +19392,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="374" hidden="1" spans="1:14">
+    <row r="374" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A374" s="2" t="s">
         <v>516</v>
       </c>
@@ -20042,7 +19436,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="375" hidden="1" spans="1:14">
+    <row r="375" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A375" s="2" t="s">
         <v>517</v>
       </c>
@@ -20086,7 +19480,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="376" hidden="1" spans="1:14">
+    <row r="376" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A376" s="2" t="s">
         <v>518</v>
       </c>
@@ -20130,7 +19524,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="377" hidden="1" spans="1:14">
+    <row r="377" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A377" s="2" t="s">
         <v>519</v>
       </c>
@@ -20174,7 +19568,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="378" hidden="1" spans="1:14">
+    <row r="378" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A378" s="2" t="s">
         <v>520</v>
       </c>
@@ -20218,7 +19612,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="379" hidden="1" spans="1:14">
+    <row r="379" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A379" s="2" t="s">
         <v>521</v>
       </c>
@@ -20262,7 +19656,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="380" hidden="1" spans="1:14">
+    <row r="380" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A380" s="2" t="s">
         <v>522</v>
       </c>
@@ -20306,7 +19700,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="381" hidden="1" spans="1:14">
+    <row r="381" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A381" s="2" t="s">
         <v>523</v>
       </c>
@@ -20350,7 +19744,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="382" hidden="1" spans="1:14">
+    <row r="382" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A382" s="2" t="s">
         <v>524</v>
       </c>
@@ -20394,7 +19788,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="383" hidden="1" spans="1:14">
+    <row r="383" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A383" s="2" t="s">
         <v>525</v>
       </c>
@@ -20438,7 +19832,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="384" hidden="1" spans="1:14">
+    <row r="384" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A384" s="2" t="s">
         <v>526</v>
       </c>
@@ -20482,7 +19876,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="385" hidden="1" spans="1:14">
+    <row r="385" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A385" s="2" t="s">
         <v>527</v>
       </c>
@@ -20526,7 +19920,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="386" hidden="1" spans="1:14">
+    <row r="386" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A386" s="2" t="s">
         <v>528</v>
       </c>
@@ -20570,7 +19964,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="387" hidden="1" spans="1:14">
+    <row r="387" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A387" s="2" t="s">
         <v>529</v>
       </c>
@@ -20614,7 +20008,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="388" hidden="1" spans="1:14">
+    <row r="388" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A388" s="2" t="s">
         <v>530</v>
       </c>
@@ -20658,7 +20052,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="389" hidden="1" spans="1:14">
+    <row r="389" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A389" s="2" t="s">
         <v>531</v>
       </c>
@@ -20702,7 +20096,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="390" hidden="1" spans="1:14">
+    <row r="390" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A390" s="2" t="s">
         <v>532</v>
       </c>
@@ -20746,7 +20140,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="391" hidden="1" spans="1:14">
+    <row r="391" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A391" s="2" t="s">
         <v>533</v>
       </c>
@@ -20790,7 +20184,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="392" hidden="1" spans="1:14">
+    <row r="392" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A392" s="2" t="s">
         <v>534</v>
       </c>
@@ -20834,7 +20228,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="393" hidden="1" spans="1:14">
+    <row r="393" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A393" s="2" t="s">
         <v>535</v>
       </c>
@@ -20878,7 +20272,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="394" hidden="1" spans="1:14">
+    <row r="394" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A394" s="2" t="s">
         <v>536</v>
       </c>
@@ -20922,7 +20316,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="395" hidden="1" spans="1:14">
+    <row r="395" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A395" s="2" t="s">
         <v>537</v>
       </c>
@@ -20966,7 +20360,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="396" hidden="1" spans="1:14">
+    <row r="396" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A396" s="2" t="s">
         <v>538</v>
       </c>
@@ -21010,7 +20404,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="397" hidden="1" spans="1:14">
+    <row r="397" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A397" s="2" t="s">
         <v>539</v>
       </c>
@@ -21054,7 +20448,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="398" hidden="1" spans="1:14">
+    <row r="398" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A398" s="2" t="s">
         <v>540</v>
       </c>
@@ -21098,7 +20492,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="399" hidden="1" spans="1:14">
+    <row r="399" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A399" s="2" t="s">
         <v>541</v>
       </c>
@@ -21142,7 +20536,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="400" hidden="1" spans="1:14">
+    <row r="400" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A400" s="2" t="s">
         <v>542</v>
       </c>
@@ -21186,7 +20580,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="401" hidden="1" spans="1:14">
+    <row r="401" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A401" s="2" t="s">
         <v>543</v>
       </c>
@@ -21230,7 +20624,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="402" hidden="1" spans="1:14">
+    <row r="402" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A402" s="2" t="s">
         <v>544</v>
       </c>
@@ -21274,7 +20668,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="403" hidden="1" spans="1:14">
+    <row r="403" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A403" s="2" t="s">
         <v>545</v>
       </c>
@@ -21318,7 +20712,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="404" hidden="1" spans="1:14">
+    <row r="404" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A404" s="2" t="s">
         <v>546</v>
       </c>
@@ -21362,7 +20756,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="405" hidden="1" spans="1:14">
+    <row r="405" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A405" s="2" t="s">
         <v>547</v>
       </c>
@@ -21406,7 +20800,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="406" hidden="1" spans="1:14">
+    <row r="406" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A406" s="2" t="s">
         <v>548</v>
       </c>
@@ -21450,7 +20844,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="407" hidden="1" spans="1:14">
+    <row r="407" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A407" s="2" t="s">
         <v>549</v>
       </c>
@@ -21494,7 +20888,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="408" hidden="1" spans="1:14">
+    <row r="408" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A408" s="2" t="s">
         <v>550</v>
       </c>
@@ -21538,7 +20932,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="409" hidden="1" spans="1:14">
+    <row r="409" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A409" s="2" t="s">
         <v>551</v>
       </c>
@@ -21582,7 +20976,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="410" hidden="1" spans="1:14">
+    <row r="410" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A410" s="2" t="s">
         <v>552</v>
       </c>
@@ -21626,7 +21020,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="411" hidden="1" spans="1:14">
+    <row r="411" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A411" s="2" t="s">
         <v>553</v>
       </c>
@@ -21670,7 +21064,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="412" hidden="1" spans="1:14">
+    <row r="412" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A412" s="2" t="s">
         <v>554</v>
       </c>
@@ -21714,7 +21108,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="413" hidden="1" spans="1:14">
+    <row r="413" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A413" s="2" t="s">
         <v>555</v>
       </c>
@@ -21758,7 +21152,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="414" hidden="1" spans="1:14">
+    <row r="414" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A414" s="2" t="s">
         <v>556</v>
       </c>
@@ -21802,7 +21196,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="415" hidden="1" spans="1:14">
+    <row r="415" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A415" s="2" t="s">
         <v>557</v>
       </c>
@@ -21846,7 +21240,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="416" hidden="1" spans="1:14">
+    <row r="416" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A416" s="2" t="s">
         <v>558</v>
       </c>
@@ -21890,7 +21284,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="417" hidden="1" spans="1:14">
+    <row r="417" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A417" s="2" t="s">
         <v>559</v>
       </c>
@@ -21934,7 +21328,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="418" hidden="1" spans="1:14">
+    <row r="418" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A418" s="2" t="s">
         <v>560</v>
       </c>
@@ -21978,7 +21372,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="419" hidden="1" spans="1:14">
+    <row r="419" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A419" s="2" t="s">
         <v>561</v>
       </c>
@@ -22022,7 +21416,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="420" hidden="1" spans="1:14">
+    <row r="420" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A420" s="2" t="s">
         <v>562</v>
       </c>
@@ -22066,7 +21460,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="421" hidden="1" spans="1:14">
+    <row r="421" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A421" s="2" t="s">
         <v>563</v>
       </c>
@@ -22110,7 +21504,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="422" hidden="1" spans="1:14">
+    <row r="422" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A422" s="2" t="s">
         <v>564</v>
       </c>
@@ -22154,7 +21548,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="423" hidden="1" spans="1:14">
+    <row r="423" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A423" s="2" t="s">
         <v>565</v>
       </c>
@@ -22198,7 +21592,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="424" hidden="1" spans="1:14">
+    <row r="424" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A424" s="2" t="s">
         <v>566</v>
       </c>
@@ -22242,7 +21636,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="425" hidden="1" spans="1:14">
+    <row r="425" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A425" s="2" t="s">
         <v>567</v>
       </c>
@@ -22286,7 +21680,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="426" hidden="1" spans="1:14">
+    <row r="426" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A426" s="2" t="s">
         <v>568</v>
       </c>
@@ -22330,7 +21724,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="427" hidden="1" spans="1:14">
+    <row r="427" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A427" s="2" t="s">
         <v>569</v>
       </c>
@@ -22374,7 +21768,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="428" hidden="1" spans="1:14">
+    <row r="428" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A428" s="2" t="s">
         <v>570</v>
       </c>
@@ -22418,7 +21812,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="429" hidden="1" spans="1:14">
+    <row r="429" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A429" s="2" t="s">
         <v>571</v>
       </c>
@@ -22462,7 +21856,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="430" hidden="1" spans="1:14">
+    <row r="430" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A430" s="2" t="s">
         <v>572</v>
       </c>
@@ -22506,7 +21900,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="431" hidden="1" spans="1:14">
+    <row r="431" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A431" s="2" t="s">
         <v>573</v>
       </c>
@@ -22550,7 +21944,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="432" hidden="1" spans="1:14">
+    <row r="432" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A432" s="2" t="s">
         <v>574</v>
       </c>
@@ -22594,7 +21988,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="433" hidden="1" spans="1:14">
+    <row r="433" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A433" s="2" t="s">
         <v>575</v>
       </c>
@@ -22638,7 +22032,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="434" hidden="1" spans="1:14">
+    <row r="434" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A434" s="2" t="s">
         <v>576</v>
       </c>
@@ -22682,7 +22076,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="435" hidden="1" spans="1:14">
+    <row r="435" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A435" s="2" t="s">
         <v>577</v>
       </c>
@@ -22726,7 +22120,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="436" hidden="1" spans="1:14">
+    <row r="436" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A436" s="2" t="s">
         <v>578</v>
       </c>
@@ -22770,7 +22164,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="437" hidden="1" spans="1:14">
+    <row r="437" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A437" s="2" t="s">
         <v>579</v>
       </c>
@@ -22814,7 +22208,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="438" hidden="1" spans="1:14">
+    <row r="438" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A438" s="2" t="s">
         <v>580</v>
       </c>
@@ -22858,7 +22252,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="439" hidden="1" spans="1:14">
+    <row r="439" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A439" s="2" t="s">
         <v>581</v>
       </c>
@@ -22902,7 +22296,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="440" hidden="1" spans="1:14">
+    <row r="440" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A440" s="2" t="s">
         <v>582</v>
       </c>
@@ -22946,7 +22340,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="441" hidden="1" spans="1:14">
+    <row r="441" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A441" s="2" t="s">
         <v>583</v>
       </c>
@@ -22990,7 +22384,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="442" hidden="1" spans="1:14">
+    <row r="442" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A442" s="2" t="s">
         <v>584</v>
       </c>
@@ -23034,7 +22428,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="443" hidden="1" spans="1:14">
+    <row r="443" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A443" s="2" t="s">
         <v>585</v>
       </c>
@@ -23078,7 +22472,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="444" hidden="1" spans="1:14">
+    <row r="444" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A444" s="2" t="s">
         <v>586</v>
       </c>
@@ -23122,7 +22516,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="445" hidden="1" spans="1:14">
+    <row r="445" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A445" s="2" t="s">
         <v>587</v>
       </c>
@@ -23166,7 +22560,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="446" hidden="1" spans="1:14">
+    <row r="446" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A446" s="2" t="s">
         <v>588</v>
       </c>
@@ -23210,7 +22604,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="447" hidden="1" spans="1:14">
+    <row r="447" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A447" s="2" t="s">
         <v>589</v>
       </c>
@@ -23254,7 +22648,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="448" hidden="1" spans="1:14">
+    <row r="448" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A448" s="2" t="s">
         <v>590</v>
       </c>
@@ -23298,7 +22692,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="449" hidden="1" spans="1:14">
+    <row r="449" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A449" s="2" t="s">
         <v>591</v>
       </c>
@@ -23342,7 +22736,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="450" hidden="1" spans="1:14">
+    <row r="450" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A450" s="2" t="s">
         <v>592</v>
       </c>
@@ -23386,7 +22780,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="451" hidden="1" spans="1:14">
+    <row r="451" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A451" s="2" t="s">
         <v>593</v>
       </c>
@@ -23430,7 +22824,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="452" hidden="1" spans="1:14">
+    <row r="452" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A452" s="2" t="s">
         <v>594</v>
       </c>
@@ -23474,7 +22868,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="453" hidden="1" spans="1:14">
+    <row r="453" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A453" s="2" t="s">
         <v>595</v>
       </c>
@@ -23518,7 +22912,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="454" hidden="1" spans="1:14">
+    <row r="454" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A454" s="2" t="s">
         <v>596</v>
       </c>
@@ -23562,7 +22956,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="455" hidden="1" spans="1:14">
+    <row r="455" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A455" s="2" t="s">
         <v>597</v>
       </c>
@@ -23606,7 +23000,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="456" hidden="1" spans="1:14">
+    <row r="456" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A456" s="2" t="s">
         <v>598</v>
       </c>
@@ -23650,7 +23044,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="457" hidden="1" spans="1:14">
+    <row r="457" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A457" s="2" t="s">
         <v>599</v>
       </c>
@@ -23694,7 +23088,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="458" hidden="1" spans="1:14">
+    <row r="458" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A458" s="2" t="s">
         <v>600</v>
       </c>
@@ -23738,7 +23132,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="459" hidden="1" spans="1:14">
+    <row r="459" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A459" s="2" t="s">
         <v>601</v>
       </c>
@@ -23782,7 +23176,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="460" hidden="1" spans="1:14">
+    <row r="460" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A460" s="2" t="s">
         <v>602</v>
       </c>
@@ -23826,7 +23220,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="461" hidden="1" spans="1:14">
+    <row r="461" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A461" s="2" t="s">
         <v>603</v>
       </c>
@@ -23870,7 +23264,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="462" hidden="1" spans="1:14">
+    <row r="462" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A462" s="2" t="s">
         <v>604</v>
       </c>
@@ -23914,7 +23308,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="463" hidden="1" spans="1:14">
+    <row r="463" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A463" s="2" t="s">
         <v>605</v>
       </c>
@@ -23958,7 +23352,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="464" hidden="1" spans="1:14">
+    <row r="464" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A464" s="2" t="s">
         <v>606</v>
       </c>
@@ -24002,7 +23396,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="465" hidden="1" spans="1:14">
+    <row r="465" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A465" s="2" t="s">
         <v>607</v>
       </c>
@@ -24046,7 +23440,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="466" hidden="1" spans="1:14">
+    <row r="466" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A466" s="2" t="s">
         <v>608</v>
       </c>
@@ -24090,7 +23484,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="467" hidden="1" spans="1:14">
+    <row r="467" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A467" s="2" t="s">
         <v>609</v>
       </c>
@@ -24134,7 +23528,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="468" hidden="1" spans="1:14">
+    <row r="468" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A468" s="2" t="s">
         <v>610</v>
       </c>
@@ -24178,7 +23572,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="469" hidden="1" spans="1:14">
+    <row r="469" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A469" s="2" t="s">
         <v>611</v>
       </c>
@@ -24222,7 +23616,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="470" hidden="1" spans="1:14">
+    <row r="470" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A470" s="2" t="s">
         <v>612</v>
       </c>
@@ -24266,7 +23660,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="471" hidden="1" spans="1:14">
+    <row r="471" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A471" s="2" t="s">
         <v>613</v>
       </c>
@@ -24310,7 +23704,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="472" hidden="1" spans="1:14">
+    <row r="472" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A472" s="2" t="s">
         <v>614</v>
       </c>
@@ -24354,7 +23748,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="473" hidden="1" spans="1:14">
+    <row r="473" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A473" s="2" t="s">
         <v>615</v>
       </c>
@@ -24398,7 +23792,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="474" hidden="1" spans="1:14">
+    <row r="474" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A474" s="2" t="s">
         <v>616</v>
       </c>
@@ -24442,7 +23836,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="475" hidden="1" spans="1:14">
+    <row r="475" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A475" s="2" t="s">
         <v>617</v>
       </c>
@@ -24486,7 +23880,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="476" hidden="1" spans="1:14">
+    <row r="476" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A476" s="2" t="s">
         <v>618</v>
       </c>
@@ -24530,7 +23924,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="477" hidden="1" spans="1:14">
+    <row r="477" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A477" s="2" t="s">
         <v>619</v>
       </c>
@@ -24574,7 +23968,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="478" hidden="1" spans="1:14">
+    <row r="478" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A478" s="2" t="s">
         <v>620</v>
       </c>
@@ -24618,7 +24012,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="479" hidden="1" spans="1:14">
+    <row r="479" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A479" s="2" t="s">
         <v>621</v>
       </c>
@@ -24662,7 +24056,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="480" hidden="1" spans="1:14">
+    <row r="480" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A480" s="2" t="s">
         <v>622</v>
       </c>
@@ -24706,7 +24100,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="481" hidden="1" spans="1:14">
+    <row r="481" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A481" s="2" t="s">
         <v>623</v>
       </c>
@@ -24750,7 +24144,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="482" hidden="1" spans="1:14">
+    <row r="482" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A482" s="2" t="s">
         <v>624</v>
       </c>
@@ -24794,7 +24188,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="483" hidden="1" spans="1:14">
+    <row r="483" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A483" s="2" t="s">
         <v>625</v>
       </c>
@@ -24838,7 +24232,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="484" hidden="1" spans="1:14">
+    <row r="484" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A484" s="2" t="s">
         <v>626</v>
       </c>
@@ -24882,7 +24276,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="485" hidden="1" spans="1:14">
+    <row r="485" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A485" s="2" t="s">
         <v>627</v>
       </c>
@@ -24926,7 +24320,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="486" hidden="1" spans="1:14">
+    <row r="486" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A486" s="2" t="s">
         <v>628</v>
       </c>
@@ -24970,7 +24364,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="487" hidden="1" spans="1:14">
+    <row r="487" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A487" s="2" t="s">
         <v>629</v>
       </c>
@@ -25014,7 +24408,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="488" hidden="1" spans="1:14">
+    <row r="488" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A488" s="2" t="s">
         <v>630</v>
       </c>
@@ -25058,7 +24452,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="489" hidden="1" spans="1:14">
+    <row r="489" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A489" s="2" t="s">
         <v>631</v>
       </c>
@@ -25102,7 +24496,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="490" hidden="1" spans="1:14">
+    <row r="490" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A490" s="2" t="s">
         <v>632</v>
       </c>
@@ -25146,7 +24540,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="491" hidden="1" spans="1:14">
+    <row r="491" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A491" s="2" t="s">
         <v>633</v>
       </c>
@@ -25190,7 +24584,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="492" hidden="1" spans="1:14">
+    <row r="492" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A492" s="2" t="s">
         <v>634</v>
       </c>
@@ -25234,7 +24628,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="493" hidden="1" spans="1:14">
+    <row r="493" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A493" s="2" t="s">
         <v>635</v>
       </c>
@@ -25278,7 +24672,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="494" hidden="1" spans="1:14">
+    <row r="494" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A494" s="2" t="s">
         <v>636</v>
       </c>
@@ -25322,7 +24716,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="495" hidden="1" spans="1:14">
+    <row r="495" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A495" s="2" t="s">
         <v>637</v>
       </c>
@@ -25366,7 +24760,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="496" hidden="1" spans="1:14">
+    <row r="496" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A496" s="2" t="s">
         <v>638</v>
       </c>
@@ -25410,7 +24804,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="497" hidden="1" spans="1:14">
+    <row r="497" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A497" s="2" t="s">
         <v>639</v>
       </c>
@@ -25454,7 +24848,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="498" hidden="1" spans="1:14">
+    <row r="498" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A498" s="2" t="s">
         <v>640</v>
       </c>
@@ -25498,7 +24892,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="499" hidden="1" spans="1:14">
+    <row r="499" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A499" s="2" t="s">
         <v>641</v>
       </c>
@@ -25542,7 +24936,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="500" hidden="1" spans="1:14">
+    <row r="500" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A500" s="2" t="s">
         <v>642</v>
       </c>
@@ -25586,7 +24980,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="501" hidden="1" spans="1:14">
+    <row r="501" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A501" s="2" t="s">
         <v>643</v>
       </c>
@@ -25630,7 +25024,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="502" hidden="1" spans="1:14">
+    <row r="502" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A502" s="2" t="s">
         <v>644</v>
       </c>
@@ -25674,7 +25068,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="503" hidden="1" spans="1:14">
+    <row r="503" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A503" s="2" t="s">
         <v>645</v>
       </c>
@@ -25718,7 +25112,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="504" hidden="1" spans="1:14">
+    <row r="504" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A504" s="2" t="s">
         <v>646</v>
       </c>
@@ -25762,7 +25156,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="505" hidden="1" spans="1:14">
+    <row r="505" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A505" s="2" t="s">
         <v>647</v>
       </c>
@@ -25806,7 +25200,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="506" hidden="1" spans="1:14">
+    <row r="506" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A506" s="2" t="s">
         <v>648</v>
       </c>
@@ -25850,7 +25244,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="507" hidden="1" spans="1:14">
+    <row r="507" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A507" s="2" t="s">
         <v>649</v>
       </c>
@@ -25894,7 +25288,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="508" hidden="1" spans="1:14">
+    <row r="508" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A508" s="2" t="s">
         <v>650</v>
       </c>
@@ -25938,7 +25332,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="509" hidden="1" spans="1:14">
+    <row r="509" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A509" s="2" t="s">
         <v>651</v>
       </c>
@@ -25982,7 +25376,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="510" hidden="1" spans="1:14">
+    <row r="510" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A510" s="2" t="s">
         <v>652</v>
       </c>
@@ -26026,7 +25420,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="511" hidden="1" spans="1:14">
+    <row r="511" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A511" s="2" t="s">
         <v>653</v>
       </c>
@@ -26070,7 +25464,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="512" hidden="1" spans="1:14">
+    <row r="512" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A512" s="2" t="s">
         <v>654</v>
       </c>
@@ -26114,7 +25508,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="513" hidden="1" spans="1:14">
+    <row r="513" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A513" s="2" t="s">
         <v>655</v>
       </c>
@@ -26158,7 +25552,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="514" hidden="1" spans="1:14">
+    <row r="514" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A514" s="2" t="s">
         <v>656</v>
       </c>
@@ -26202,7 +25596,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="515" hidden="1" spans="1:14">
+    <row r="515" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A515" s="2" t="s">
         <v>657</v>
       </c>
@@ -26246,7 +25640,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="516" hidden="1" spans="1:14">
+    <row r="516" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A516" s="2" t="s">
         <v>658</v>
       </c>
@@ -26290,7 +25684,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="517" hidden="1" spans="1:14">
+    <row r="517" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A517" s="2" t="s">
         <v>659</v>
       </c>
@@ -26334,7 +25728,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="518" hidden="1" spans="1:14">
+    <row r="518" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A518" s="2" t="s">
         <v>660</v>
       </c>
@@ -26378,7 +25772,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="519" hidden="1" spans="1:14">
+    <row r="519" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A519" s="2" t="s">
         <v>661</v>
       </c>
@@ -26422,7 +25816,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="520" spans="1:15">
+    <row r="520" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A520" s="2" t="s">
         <v>662</v>
       </c>
@@ -26469,7 +25863,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="521" hidden="1" spans="1:14">
+    <row r="521" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A521" s="2" t="s">
         <v>664</v>
       </c>
@@ -26513,7 +25907,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="522" hidden="1" spans="1:14">
+    <row r="522" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A522" s="2" t="s">
         <v>665</v>
       </c>
@@ -26557,7 +25951,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="523" hidden="1" spans="1:14">
+    <row r="523" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A523" s="2" t="s">
         <v>666</v>
       </c>
@@ -26601,7 +25995,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="524" hidden="1" spans="1:14">
+    <row r="524" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A524" s="2" t="s">
         <v>667</v>
       </c>
@@ -26645,7 +26039,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="525" hidden="1" spans="1:14">
+    <row r="525" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A525" s="2" t="s">
         <v>668</v>
       </c>
@@ -26689,7 +26083,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="526" hidden="1" spans="1:14">
+    <row r="526" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A526" s="2" t="s">
         <v>669</v>
       </c>
@@ -26733,7 +26127,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="527" hidden="1" spans="1:14">
+    <row r="527" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A527" s="2" t="s">
         <v>670</v>
       </c>
@@ -26777,7 +26171,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="528" hidden="1" spans="1:14">
+    <row r="528" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A528" s="2" t="s">
         <v>671</v>
       </c>
@@ -26821,7 +26215,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="529" hidden="1" spans="1:14">
+    <row r="529" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A529" s="2" t="s">
         <v>672</v>
       </c>
@@ -26865,7 +26259,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="530" hidden="1" spans="1:14">
+    <row r="530" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A530" s="2" t="s">
         <v>673</v>
       </c>
@@ -26909,7 +26303,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="531" hidden="1" spans="1:14">
+    <row r="531" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A531" s="2" t="s">
         <v>674</v>
       </c>
@@ -26953,7 +26347,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="532" hidden="1" spans="1:14">
+    <row r="532" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A532" s="2" t="s">
         <v>675</v>
       </c>
@@ -26997,7 +26391,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="533" hidden="1" spans="1:14">
+    <row r="533" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A533" s="2" t="s">
         <v>676</v>
       </c>
@@ -27041,7 +26435,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="534" hidden="1" spans="1:14">
+    <row r="534" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A534" s="2" t="s">
         <v>677</v>
       </c>
@@ -27085,7 +26479,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="535" hidden="1" spans="1:14">
+    <row r="535" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A535" s="2" t="s">
         <v>678</v>
       </c>
@@ -27129,7 +26523,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="536" hidden="1" spans="1:14">
+    <row r="536" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A536" s="2" t="s">
         <v>679</v>
       </c>
@@ -27173,7 +26567,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="537" hidden="1" spans="1:14">
+    <row r="537" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A537" s="2" t="s">
         <v>680</v>
       </c>
@@ -27217,7 +26611,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="538" spans="1:15">
+    <row r="538" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A538" s="2" t="s">
         <v>681</v>
       </c>
@@ -27264,7 +26658,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="539" hidden="1" spans="1:14">
+    <row r="539" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A539" s="2" t="s">
         <v>683</v>
       </c>
@@ -27308,7 +26702,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="540" spans="1:15">
+    <row r="540" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A540" s="2" t="s">
         <v>684</v>
       </c>
@@ -27355,7 +26749,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="541" hidden="1" spans="1:14">
+    <row r="541" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A541" s="2" t="s">
         <v>686</v>
       </c>
@@ -27399,7 +26793,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="542" spans="1:15">
+    <row r="542" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A542" s="2" t="s">
         <v>687</v>
       </c>
@@ -27446,7 +26840,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="543" hidden="1" spans="1:14">
+    <row r="543" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A543" s="2" t="s">
         <v>688</v>
       </c>
@@ -27490,7 +26884,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="544" hidden="1" spans="1:14">
+    <row r="544" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A544" s="2" t="s">
         <v>689</v>
       </c>
@@ -27534,7 +26928,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="545" hidden="1" spans="1:14">
+    <row r="545" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A545" s="2" t="s">
         <v>690</v>
       </c>
@@ -27578,7 +26972,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="546" hidden="1" spans="1:14">
+    <row r="546" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A546" s="2" t="s">
         <v>691</v>
       </c>
@@ -27622,7 +27016,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="547" hidden="1" spans="1:14">
+    <row r="547" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A547" s="2" t="s">
         <v>692</v>
       </c>
@@ -27666,7 +27060,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="548" hidden="1" spans="1:14">
+    <row r="548" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A548" s="2" t="s">
         <v>693</v>
       </c>
@@ -27710,7 +27104,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="549" hidden="1" spans="1:14">
+    <row r="549" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A549" s="2" t="s">
         <v>694</v>
       </c>
@@ -27754,7 +27148,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="550" hidden="1" spans="1:14">
+    <row r="550" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A550" s="2" t="s">
         <v>695</v>
       </c>
@@ -27798,7 +27192,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="551" hidden="1" spans="1:14">
+    <row r="551" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A551" s="2" t="s">
         <v>696</v>
       </c>
@@ -27842,7 +27236,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="552" hidden="1" spans="1:14">
+    <row r="552" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A552" s="2" t="s">
         <v>697</v>
       </c>
@@ -27886,7 +27280,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="553" hidden="1" spans="1:14">
+    <row r="553" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A553" s="2" t="s">
         <v>698</v>
       </c>
@@ -27930,7 +27324,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="554" hidden="1" spans="1:14">
+    <row r="554" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A554" s="2" t="s">
         <v>699</v>
       </c>
@@ -27974,7 +27368,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="555" hidden="1" spans="1:14">
+    <row r="555" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A555" s="2" t="s">
         <v>700</v>
       </c>
@@ -28018,7 +27412,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="556" spans="1:15">
+    <row r="556" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A556" s="2" t="s">
         <v>701</v>
       </c>
@@ -28065,7 +27459,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="557" hidden="1" spans="1:14">
+    <row r="557" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A557" s="2" t="s">
         <v>704</v>
       </c>
@@ -28109,7 +27503,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="558" hidden="1" spans="1:14">
+    <row r="558" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A558" s="2" t="s">
         <v>705</v>
       </c>
@@ -28153,7 +27547,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="559" hidden="1" spans="1:14">
+    <row r="559" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A559" s="2" t="s">
         <v>706</v>
       </c>
@@ -28197,7 +27591,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="560" spans="1:15">
+    <row r="560" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A560" s="2" t="s">
         <v>707</v>
       </c>
@@ -28244,7 +27638,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="561" hidden="1" spans="1:14">
+    <row r="561" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A561" s="2" t="s">
         <v>710</v>
       </c>
@@ -28288,7 +27682,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="562" hidden="1" spans="1:14">
+    <row r="562" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A562" s="2" t="s">
         <v>711</v>
       </c>
@@ -28332,7 +27726,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="563" hidden="1" spans="1:14">
+    <row r="563" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A563" s="2" t="s">
         <v>712</v>
       </c>
@@ -28376,7 +27770,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="564" hidden="1" spans="1:14">
+    <row r="564" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A564" s="2" t="s">
         <v>713</v>
       </c>
@@ -28420,7 +27814,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="565" hidden="1" spans="1:14">
+    <row r="565" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A565" s="2" t="s">
         <v>714</v>
       </c>
@@ -28464,7 +27858,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="566" hidden="1" spans="1:14">
+    <row r="566" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A566" s="2" t="s">
         <v>715</v>
       </c>
@@ -28508,7 +27902,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="567" hidden="1" spans="1:14">
+    <row r="567" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A567" s="2" t="s">
         <v>716</v>
       </c>
@@ -28552,7 +27946,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="568" hidden="1" spans="1:14">
+    <row r="568" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A568" s="2" t="s">
         <v>717</v>
       </c>
@@ -28596,7 +27990,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="569" hidden="1" spans="1:14">
+    <row r="569" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A569" s="2" t="s">
         <v>718</v>
       </c>
@@ -28640,7 +28034,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="570" hidden="1" spans="1:14">
+    <row r="570" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A570" s="2" t="s">
         <v>719</v>
       </c>
@@ -28684,7 +28078,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="571" hidden="1" spans="1:14">
+    <row r="571" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A571" s="2" t="s">
         <v>720</v>
       </c>
@@ -28728,7 +28122,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="572" hidden="1" spans="1:14">
+    <row r="572" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A572" s="2" t="s">
         <v>721</v>
       </c>
@@ -28772,7 +28166,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="573" hidden="1" spans="1:14">
+    <row r="573" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A573" s="2" t="s">
         <v>722</v>
       </c>
@@ -28816,7 +28210,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="574" hidden="1" spans="1:14">
+    <row r="574" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A574" s="2" t="s">
         <v>723</v>
       </c>
@@ -28860,7 +28254,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="575" hidden="1" spans="1:14">
+    <row r="575" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A575" s="2" t="s">
         <v>724</v>
       </c>
@@ -28904,7 +28298,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="576" hidden="1" spans="1:14">
+    <row r="576" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A576" s="2" t="s">
         <v>725</v>
       </c>
@@ -28948,7 +28342,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="577" hidden="1" spans="1:14">
+    <row r="577" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A577" s="2" t="s">
         <v>726</v>
       </c>
@@ -28992,7 +28386,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="578" hidden="1" spans="1:14">
+    <row r="578" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A578" s="2" t="s">
         <v>727</v>
       </c>
@@ -29036,7 +28430,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="579" hidden="1" spans="1:14">
+    <row r="579" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A579" s="2" t="s">
         <v>728</v>
       </c>
@@ -29080,7 +28474,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="580" hidden="1" spans="1:14">
+    <row r="580" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A580" s="2" t="s">
         <v>729</v>
       </c>
@@ -29124,7 +28518,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="581" hidden="1" spans="1:14">
+    <row r="581" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A581" s="2" t="s">
         <v>730</v>
       </c>
@@ -29168,7 +28562,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="582" hidden="1" spans="1:14">
+    <row r="582" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A582" s="2" t="s">
         <v>731</v>
       </c>
@@ -29212,7 +28606,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="583" hidden="1" spans="1:14">
+    <row r="583" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A583" s="2" t="s">
         <v>732</v>
       </c>
@@ -29256,7 +28650,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="584" hidden="1" spans="1:14">
+    <row r="584" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A584" s="2" t="s">
         <v>733</v>
       </c>
@@ -29300,7 +28694,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="585" hidden="1" spans="1:14">
+    <row r="585" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A585" s="2" t="s">
         <v>734</v>
       </c>
@@ -29344,7 +28738,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="586" hidden="1" spans="1:14">
+    <row r="586" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A586" s="2" t="s">
         <v>735</v>
       </c>
@@ -29388,7 +28782,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="587" hidden="1" spans="1:14">
+    <row r="587" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A587" s="2" t="s">
         <v>736</v>
       </c>
@@ -29432,7 +28826,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="588" hidden="1" spans="1:14">
+    <row r="588" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A588" s="2" t="s">
         <v>737</v>
       </c>
@@ -29476,7 +28870,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="589" hidden="1" spans="1:14">
+    <row r="589" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A589" s="2" t="s">
         <v>738</v>
       </c>
@@ -29520,7 +28914,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="590" hidden="1" spans="1:14">
+    <row r="590" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A590" s="2" t="s">
         <v>739</v>
       </c>
@@ -29564,7 +28958,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="591" hidden="1" spans="1:14">
+    <row r="591" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A591" s="2" t="s">
         <v>740</v>
       </c>
@@ -29608,7 +29002,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="592" hidden="1" spans="1:14">
+    <row r="592" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A592" s="2" t="s">
         <v>741</v>
       </c>
@@ -29652,7 +29046,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="593" hidden="1" spans="1:14">
+    <row r="593" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A593" s="2" t="s">
         <v>742</v>
       </c>
@@ -29696,7 +29090,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="594" hidden="1" spans="1:14">
+    <row r="594" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A594" s="2" t="s">
         <v>743</v>
       </c>
@@ -29740,7 +29134,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="595" hidden="1" spans="1:14">
+    <row r="595" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A595" s="2" t="s">
         <v>744</v>
       </c>
@@ -29784,7 +29178,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="596" hidden="1" spans="1:14">
+    <row r="596" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A596" s="2" t="s">
         <v>745</v>
       </c>
@@ -29828,7 +29222,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="597" hidden="1" spans="1:14">
+    <row r="597" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A597" s="2" t="s">
         <v>746</v>
       </c>
@@ -29872,7 +29266,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="598" hidden="1" spans="1:14">
+    <row r="598" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A598" s="2" t="s">
         <v>747</v>
       </c>
@@ -29916,7 +29310,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="599" hidden="1" spans="1:14">
+    <row r="599" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A599" s="2" t="s">
         <v>748</v>
       </c>
@@ -29960,7 +29354,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="600" hidden="1" spans="1:14">
+    <row r="600" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A600" s="2" t="s">
         <v>749</v>
       </c>
@@ -30004,7 +29398,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="601" hidden="1" spans="1:14">
+    <row r="601" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A601" s="2" t="s">
         <v>750</v>
       </c>
@@ -30048,7 +29442,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="602" hidden="1" spans="1:14">
+    <row r="602" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A602" s="2" t="s">
         <v>751</v>
       </c>
@@ -30092,7 +29486,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="603" hidden="1" spans="1:14">
+    <row r="603" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A603" s="2" t="s">
         <v>752</v>
       </c>
@@ -30136,7 +29530,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="604" hidden="1" spans="1:14">
+    <row r="604" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A604" s="2" t="s">
         <v>753</v>
       </c>
@@ -30180,7 +29574,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="605" hidden="1" spans="1:14">
+    <row r="605" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A605" s="2" t="s">
         <v>754</v>
       </c>
@@ -30224,7 +29618,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="606" hidden="1" spans="1:14">
+    <row r="606" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A606" s="2" t="s">
         <v>755</v>
       </c>
@@ -30268,7 +29662,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="607" hidden="1" spans="1:14">
+    <row r="607" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A607" s="2" t="s">
         <v>756</v>
       </c>
@@ -30312,7 +29706,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="608" hidden="1" spans="1:14">
+    <row r="608" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A608" s="2" t="s">
         <v>757</v>
       </c>
@@ -30356,7 +29750,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="609" hidden="1" spans="1:14">
+    <row r="609" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A609" s="2" t="s">
         <v>758</v>
       </c>
@@ -30400,7 +29794,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="610" hidden="1" spans="1:14">
+    <row r="610" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A610" s="2" t="s">
         <v>759</v>
       </c>
@@ -30444,7 +29838,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="611" hidden="1" spans="1:14">
+    <row r="611" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A611" s="2" t="s">
         <v>760</v>
       </c>
@@ -30488,7 +29882,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="612" hidden="1" spans="1:14">
+    <row r="612" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A612" s="2" t="s">
         <v>761</v>
       </c>
@@ -30532,7 +29926,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="613" hidden="1" spans="1:14">
+    <row r="613" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A613" s="2" t="s">
         <v>762</v>
       </c>
@@ -30576,7 +29970,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="614" hidden="1" spans="1:14">
+    <row r="614" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A614" s="2" t="s">
         <v>763</v>
       </c>
@@ -30620,7 +30014,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="615" hidden="1" spans="1:14">
+    <row r="615" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A615" s="2" t="s">
         <v>764</v>
       </c>
@@ -30664,7 +30058,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="616" hidden="1" spans="1:14">
+    <row r="616" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A616" s="2" t="s">
         <v>765</v>
       </c>
@@ -30708,7 +30102,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="617" hidden="1" spans="1:14">
+    <row r="617" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A617" s="2" t="s">
         <v>766</v>
       </c>
@@ -30752,7 +30146,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="618" hidden="1" spans="1:14">
+    <row r="618" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
       <c r="A618" s="2" t="s">
         <v>767</v>
       </c>
@@ -30797,15 +30191,1017 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O618" etc:filterBottomFollowUsedRange="0">
+  <autoFilter ref="A1:O618" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="reols"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="1">
-      <customFilters>
-        <customFilter operator="equal" val="Y"/>
-      </customFilters>
+      <filters>
+        <filter val="Y"/>
+      </filters>
     </filterColumn>
-    <extLst/>
   </autoFilter>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F353D8-7EFB-4713-9CA6-32CAE141C2E6}">
+  <dimension ref="A1:O21"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A2" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N2" s="4">
+        <v>44916</v>
+      </c>
+      <c r="O2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A3" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" s="4">
+        <v>44916</v>
+      </c>
+      <c r="O3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A4" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" s="4">
+        <v>44811</v>
+      </c>
+      <c r="O4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A5" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N5" s="4">
+        <v>44811</v>
+      </c>
+      <c r="O5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A6" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N6" s="4">
+        <v>44811</v>
+      </c>
+      <c r="O6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A7" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N7" s="4">
+        <v>44811</v>
+      </c>
+      <c r="O7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A8" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N8" s="4">
+        <v>44811</v>
+      </c>
+      <c r="O8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A9" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N9" s="4">
+        <v>44811</v>
+      </c>
+      <c r="O9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N10" s="4">
+        <v>44811</v>
+      </c>
+      <c r="O10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A11" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N11" s="4">
+        <v>44811</v>
+      </c>
+      <c r="O11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A12" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N12" s="4">
+        <v>44811</v>
+      </c>
+      <c r="O12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A13" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N13" s="4">
+        <v>44811</v>
+      </c>
+      <c r="O13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A14" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="N14" s="4">
+        <v>43401</v>
+      </c>
+      <c r="O14" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A15" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="N15" s="4">
+        <v>44811</v>
+      </c>
+      <c r="O15" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A16" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N16" s="4">
+        <v>44836</v>
+      </c>
+      <c r="O16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A17" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N17" s="4">
+        <v>44629</v>
+      </c>
+      <c r="O17" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A18" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="N18" s="4">
+        <v>44407</v>
+      </c>
+      <c r="O18" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A19" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N19" s="4">
+        <v>45068</v>
+      </c>
+      <c r="O19" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A20" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O20" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A21" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="N21" s="4">
+        <v>45067</v>
+      </c>
+      <c r="O21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>